--- a/Feed.xlsx
+++ b/Feed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jvaud\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B810C4C6-16D7-4066-B1FE-7CF839C9D05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC549027-6A2F-45E7-87D4-11062BC4C180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7513" uniqueCount="2235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7516" uniqueCount="2236">
   <si>
     <t>RSS_FEEDS</t>
   </si>
@@ -6738,6 +6738,9 @@
   </si>
   <si>
     <t>Tethers</t>
+  </si>
+  <si>
+    <t>Odin</t>
   </si>
 </sst>
 </file>
@@ -7062,7 +7065,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G2492"/>
+  <dimension ref="A1:G2493"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
@@ -34643,6 +34646,17 @@
       </c>
       <c r="D2492" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="2493" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2493" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2493" s="6" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D2493" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
